--- a/backend/data/financials_by_company/1957.HK.xlsx
+++ b/backend/data/financials_by_company/1957.HK.xlsx
@@ -4024,10 +4024,8 @@
           <t>Johor Bahru</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>81100</t>
-        </is>
+      <c r="D2" t="n">
+        <v>81100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4233,7 +4231,7 @@
         <v>-707000</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
         <v>0.159</v>
@@ -4464,7 +4462,7 @@
         <v>1</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
         <v>0.015659988</v>
